--- a/Cases.xlsx
+++ b/Cases.xlsx
@@ -906,8 +906,10 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Java UI-покрытие</t>
+        </is>
       </c>
     </row>
     <row r="2" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -929,8 +931,10 @@
       <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: AuthTest.successfulLogin</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -952,8 +956,10 @@
       <c r="F3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: AuthTest.loginWithEmptyLogin</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -975,8 +981,10 @@
       <c r="F4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: AuthTest.loginWithEmptyPassword</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -998,8 +1006,10 @@
       <c r="F5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>12</v>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: AuthTest.loginWithUnregisteredUser</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1021,8 +1031,10 @@
       <c r="F6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>12</v>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NavigationTest.logOut</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1044,8 +1056,10 @@
       <c r="F7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>12</v>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NavigationTest.openNewsFromMenu</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1067,8 +1081,10 @@
       <c r="F8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>12</v>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NavigationTest.openThematicQuotes</t>
+        </is>
       </c>
     </row>
     <row r="9" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1090,8 +1106,10 @@
       <c r="F9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>12</v>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NavigationTest.openAllNews</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1113,8 +1131,10 @@
       <c r="F10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>12</v>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsFilterTest.sortNewsByPublishDate</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1136,8 +1156,10 @@
       <c r="F11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>12</v>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsFilterTest.filterByAnnouncement</t>
+        </is>
       </c>
     </row>
     <row r="12" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1159,8 +1181,10 @@
       <c r="F12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>12</v>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsFilterTest.filterByBirthday</t>
+        </is>
       </c>
     </row>
     <row r="13" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1182,8 +1206,10 @@
       <c r="F13" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>12</v>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsFilterTest.filterBySalary</t>
+        </is>
       </c>
     </row>
     <row r="14" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1205,8 +1231,10 @@
       <c r="F14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>12</v>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsFilterTest.filterByUnion</t>
+        </is>
       </c>
     </row>
     <row r="15" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1228,8 +1256,10 @@
       <c r="F15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>12</v>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsFilterTest.filterByHoliday</t>
+        </is>
       </c>
     </row>
     <row r="16" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1251,8 +1281,10 @@
       <c r="F16" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>12</v>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsFilterTest.filterByMassage</t>
+        </is>
       </c>
     </row>
     <row r="17" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1274,8 +1306,10 @@
       <c r="F17" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>12</v>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsFilterTest.filterByGratitude</t>
+        </is>
       </c>
     </row>
     <row r="18" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1297,8 +1331,10 @@
       <c r="F18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>12</v>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsFilterTest.filterByHelp</t>
+        </is>
       </c>
     </row>
     <row r="19" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1320,8 +1356,10 @@
       <c r="F19" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>12</v>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsFilterTest.applyFilterWithoutCategory</t>
+        </is>
       </c>
     </row>
     <row r="20" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1343,8 +1381,10 @@
       <c r="F20" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>12</v>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsFilterTest.resetFilter</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1366,8 +1406,10 @@
       <c r="F21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>12</v>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.sortNewsInControlPanel</t>
+        </is>
       </c>
     </row>
     <row r="22" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1389,8 +1431,10 @@
       <c r="F22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>12</v>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.viewNewsInControlPanel</t>
+        </is>
       </c>
     </row>
     <row r="23" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1412,8 +1456,10 @@
       <c r="F23" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>12</v>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.deleteNews</t>
+        </is>
       </c>
     </row>
     <row r="24" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1435,8 +1481,10 @@
       <c r="F24" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>12</v>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.editNews</t>
+        </is>
       </c>
     </row>
     <row r="25" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1458,8 +1506,10 @@
       <c r="F25" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>12</v>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.changeNewsStatusToInactive</t>
+        </is>
       </c>
     </row>
     <row r="26" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1481,8 +1531,10 @@
       <c r="F26" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>12</v>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.filterActiveNews</t>
+        </is>
       </c>
     </row>
     <row r="27" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1504,8 +1556,10 @@
       <c r="F27" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>12</v>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.filterInactiveNews</t>
+        </is>
       </c>
     </row>
     <row r="28" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1527,8 +1581,10 @@
       <c r="F28" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>12</v>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.createNews</t>
+        </is>
       </c>
     </row>
     <row r="29" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1550,8 +1606,10 @@
       <c r="F29" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>12</v>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.createNewsWithoutCategory</t>
+        </is>
       </c>
     </row>
     <row r="30" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1573,8 +1631,10 @@
       <c r="F30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>12</v>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.createNewsWithoutDate</t>
+        </is>
       </c>
     </row>
     <row r="31" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1596,8 +1656,10 @@
       <c r="F31" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>12</v>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.createNewsWithoutTime</t>
+        </is>
       </c>
     </row>
     <row r="32" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1619,8 +1681,10 @@
       <c r="F32" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>12</v>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.createNewsWithoutDescription</t>
+        </is>
       </c>
     </row>
     <row r="33" spans="1:7" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
@@ -1642,8 +1706,10 @@
       <c r="F33" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>12</v>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: NewsTest.createNewsWithoutTitle</t>
+        </is>
       </c>
     </row>
     <row r="34" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -1665,8 +1731,10 @@
       <c r="F34" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>12</v>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Java UI: QuotesTest.expandAndCollapseQuote</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1696,48 +1764,60 @@
       <c r="A2" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="5">
-        <v>32</v>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5">
-        <v>19</v>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="5">
-        <v>11</v>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="5">
-        <v>2</v>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>121</v>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>«Наша Миссия» проверяется кейсами тематических цитат.</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>123</v>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Добавлены и уточнены сценарии тематических цитат, Main, ALL NEWS и перехода через меню.</t>
+        </is>
       </c>
     </row>
   </sheetData>
